--- a/Matlab - Simulink/Tablas/valores_curva_NL.xlsx
+++ b/Matlab - Simulink/Tablas/valores_curva_NL.xlsx
@@ -13,7 +13,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
+  <si>
+    <t>Tiempo_s</t>
+  </si>
+  <si>
+    <t>Omega_rad_s</t>
+  </si>
+  <si>
+    <t>Tm_Nm</t>
+  </si>
   <si>
     <t>Tiempo_s</t>
   </si>
@@ -86,13 +167,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -108,13 +189,13 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.10009999999999999</v>
       </c>
       <c r="B3" s="0">
-        <v>0.086450162605732073</v>
+        <v>0.065143541380156128</v>
       </c>
       <c r="C3" s="0">
-        <v>0.02027004891394479</v>
+        <v>0.024877841841798615</v>
       </c>
     </row>
     <row r="4">
@@ -122,10 +203,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="B4" s="0">
-        <v>401.28553105894281</v>
+        <v>401.47873111740444</v>
       </c>
       <c r="C4" s="0">
-        <v>0.021594766761789144</v>
+        <v>0.02083993221585842</v>
       </c>
     </row>
     <row r="5">
@@ -133,10 +214,10 @@
         <v>0.5</v>
       </c>
       <c r="B5" s="0">
-        <v>390.51367667938359</v>
+        <v>383.30177196455395</v>
       </c>
       <c r="C5" s="0">
-        <v>0.079778595274906064</v>
+        <v>0.080162653225577168</v>
       </c>
     </row>
     <row r="6">
@@ -144,10 +225,10 @@
         <v>0.69999999999999996</v>
       </c>
       <c r="B6" s="0">
-        <v>414.46699382537253</v>
+        <v>416.09846671878347</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.024470910712518893</v>
+        <v>-0.024327164336630056</v>
       </c>
     </row>
     <row r="7">
@@ -155,10 +236,10 @@
         <v>0.90000000000000002</v>
       </c>
       <c r="B7" s="0">
-        <v>8.6103304765821527</v>
+        <v>9.3405661495924406</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.033793881550469813</v>
+        <v>-0.03320427322229378</v>
       </c>
     </row>
     <row r="8">
@@ -166,10 +247,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B8" s="0">
-        <v>-4.6675635054231543</v>
+        <v>-5.9351894151370557</v>
       </c>
       <c r="C8" s="0">
-        <v>0.018312834979332362</v>
+        <v>0.018327162011894809</v>
       </c>
     </row>
     <row r="9">
@@ -177,10 +258,10 @@
         <v>1.3</v>
       </c>
       <c r="B9" s="0">
-        <v>-412.62623515009159</v>
+        <v>-412.18843966809135</v>
       </c>
       <c r="C9" s="0">
-        <v>0.011519333020661778</v>
+        <v>0.011016948874982222</v>
       </c>
     </row>
     <row r="10">
@@ -188,10 +269,10 @@
         <v>1.5</v>
       </c>
       <c r="B10" s="0">
-        <v>-422.48085785211202</v>
+        <v>-425.44559221396094</v>
       </c>
       <c r="C10" s="0">
-        <v>0.055643730638075935</v>
+        <v>0.055401699054441415</v>
       </c>
     </row>
     <row r="11">
@@ -199,10 +280,10 @@
         <v>1.7</v>
       </c>
       <c r="B11" s="0">
-        <v>-392.45810353960383</v>
+        <v>-388.30991644003274</v>
       </c>
       <c r="C11" s="0">
-        <v>-0.060839412052089342</v>
+        <v>-0.06074588263964302</v>
       </c>
     </row>
     <row r="12">
@@ -210,10 +291,10 @@
         <v>1.8999999999999999</v>
       </c>
       <c r="B12" s="0">
-        <v>11.988728254092155</v>
+        <v>17.130008560640569</v>
       </c>
       <c r="C12" s="0">
-        <v>-0.051659291819668017</v>
+        <v>-0.052152954985104111</v>
       </c>
     </row>
   </sheetData>
